--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.95073</v>
+        <v>17.18367</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49678</v>
+        <v>16.57488</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80534</v>
+        <v>16.60273</v>
       </c>
       <c r="F2" t="n">
-        <v>41.52328</v>
+        <v>41.92967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05132</v>
+        <v>0.0502</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80027</v>
+        <v>1.8082</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.0388</v>
+        <v>16.8519</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62875</v>
+        <v>16.66632</v>
       </c>
       <c r="E3" t="n">
-        <v>16.97471</v>
+        <v>16.7249</v>
       </c>
       <c r="F3" t="n">
-        <v>42.33238</v>
+        <v>42.82509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05057</v>
+        <v>0.05046</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83516</v>
+        <v>1.81292</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.14786</v>
+        <v>16.61271</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75302</v>
+        <v>16.57423</v>
       </c>
       <c r="E4" t="n">
-        <v>16.65012</v>
+        <v>16.61197</v>
       </c>
       <c r="F4" t="n">
-        <v>43.41543</v>
+        <v>43.1818</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04991</v>
+        <v>0.05096</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80227</v>
+        <v>1.81108</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.02762</v>
+        <v>16.85995</v>
       </c>
       <c r="D6" t="n">
-        <v>16.12382</v>
+        <v>15.90307</v>
       </c>
       <c r="E6" t="n">
-        <v>16.4469</v>
+        <v>16.67487</v>
       </c>
       <c r="F6" t="n">
-        <v>21.83085</v>
+        <v>22.36636</v>
       </c>
       <c r="G6" t="n">
-        <v>33.29701</v>
+        <v>34.25027</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.50521</v>
+        <v>16.70702</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24022</v>
+        <v>16.16623</v>
       </c>
       <c r="E7" t="n">
-        <v>16.17175</v>
+        <v>16.47944</v>
       </c>
       <c r="F7" t="n">
-        <v>21.60003</v>
+        <v>21.43116</v>
       </c>
       <c r="G7" t="n">
-        <v>34.51557</v>
+        <v>34.24256</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.46095</v>
+        <v>16.47117</v>
       </c>
       <c r="D8" t="n">
-        <v>15.75727</v>
+        <v>16.2308</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21901</v>
+        <v>16.40984</v>
       </c>
       <c r="F8" t="n">
-        <v>21.93376</v>
+        <v>22.07792</v>
       </c>
       <c r="G8" t="n">
-        <v>33.53843</v>
+        <v>33.79747</v>
       </c>
     </row>
   </sheetData>
